--- a/Packages/cn.etetet.twsunit/Luban/Config/Base/__beans__.xlsx
+++ b/Packages/cn.etetet.twsunit/Luban/Config/Base/__beans__.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20445" windowHeight="7440"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -105,7 +105,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -123,13 +123,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -241,13 +234,6 @@
       <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -592,133 +578,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -732,7 +718,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="22" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1056,6 +1042,11 @@
   <sheetPr/>
   <dimension ref="A1:P3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="2"/>
+  <cols>
+    <col min="2" max="2" width="33.75" customWidth="1"/>
+    <col min="4" max="4" width="9.625" customWidth="1"/>
+    <col min="10" max="10" width="15.625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">

--- a/Packages/cn.etetet.twsunit/Luban/Config/Base/__beans__.xlsx
+++ b/Packages/cn.etetet.twsunit/Luban/Config/Base/__beans__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="28">
   <si>
     <t>##var</t>
   </si>
@@ -93,6 +93,24 @@
   </si>
   <si>
     <t>字段变体</t>
+  </si>
+  <si>
+    <t>cn.etetet.twsmmo.InitCastData</t>
+  </si>
+  <si>
+    <t>InitCastId</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>InitCastPos</t>
+  </si>
+  <si>
+    <t>(list#sep=,),float</t>
+  </si>
+  <si>
+    <t>InitCastScale</t>
   </si>
 </sst>
 </file>
@@ -1040,12 +1058,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="2"/>
+  <dimension ref="A1:P6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
   <cols>
     <col min="2" max="2" width="33.75" customWidth="1"/>
     <col min="4" max="4" width="9.625" customWidth="1"/>
     <col min="10" max="10" width="15.625" customWidth="1"/>
+    <col min="12" max="12" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -1141,6 +1160,33 @@
         <v>21</v>
       </c>
     </row>
+    <row r="4" spans="2:12">
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="10:12">
+      <c r="J5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="10:12">
+      <c r="J6" t="s">
+        <v>27</v>
+      </c>
+      <c r="L6" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="J1:P1"/>

--- a/Packages/cn.etetet.twsunit/Luban/Config/Base/__beans__.xlsx
+++ b/Packages/cn.etetet.twsunit/Luban/Config/Base/__beans__.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowWidth="21600"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
   <si>
     <t>##var</t>
   </si>
@@ -93,24 +93,6 @@
   </si>
   <si>
     <t>字段变体</t>
-  </si>
-  <si>
-    <t>cn.etetet.twsmmo.InitCastData</t>
-  </si>
-  <si>
-    <t>InitCastId</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>InitCastPos</t>
-  </si>
-  <si>
-    <t>(list#sep=,),float</t>
-  </si>
-  <si>
-    <t>InitCastScale</t>
   </si>
 </sst>
 </file>
@@ -726,7 +708,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -738,6 +720,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1058,16 +1043,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
+  <dimension ref="A1:V3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="2"/>
   <cols>
     <col min="2" max="2" width="33.75" customWidth="1"/>
     <col min="4" max="4" width="9.625" customWidth="1"/>
     <col min="10" max="10" width="15.625" customWidth="1"/>
     <col min="12" max="12" width="14.625" customWidth="1"/>
+    <col min="17" max="17" width="12.625" customWidth="1"/>
+    <col min="18" max="18" width="13" customWidth="1"/>
+    <col min="19" max="19" width="10.125" customWidth="1"/>
+    <col min="20" max="20" width="25.75" customWidth="1"/>
+    <col min="21" max="21" width="15" customWidth="1"/>
+    <col min="22" max="22" width="25.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:22">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1104,8 +1095,14 @@
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="4"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4"/>
+      <c r="U1" s="4"/>
+      <c r="V1" s="4"/>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:22">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1130,6 +1127,10 @@
       <c r="P2" s="3" t="s">
         <v>12</v>
       </c>
+      <c r="S2" s="4"/>
+      <c r="T2" s="4"/>
+      <c r="U2" s="4"/>
+      <c r="V2" s="4"/>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" t="s">
@@ -1160,36 +1161,11 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="2:12">
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="J4" t="s">
-        <v>23</v>
-      </c>
-      <c r="L4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="10:12">
-      <c r="J5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="10:12">
-      <c r="J6" t="s">
-        <v>27</v>
-      </c>
-      <c r="L6" t="s">
-        <v>26</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
     <mergeCell ref="J1:P1"/>
+    <mergeCell ref="Q1:V1"/>
+    <mergeCell ref="S2:V2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
